--- a/outputs/daily/hr_rankings_2026-07-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-16.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -804,11 +804,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -831,7 +831,7 @@
         <v>64.8</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -841,39 +841,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1018,7 +1014,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1084,7 +1080,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1108,7 +1104,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1122,7 +1118,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1135,7 +1131,7 @@
         <v>64.8</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1145,39 +1141,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1322,7 +1314,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1388,7 +1380,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1412,7 +1404,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.7</v>
+        <v>57.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1426,7 +1418,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1439,7 +1431,7 @@
         <v>64.8</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>75</v>
@@ -1449,39 +1441,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1626,7 +1614,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1692,7 +1680,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1716,7 +1704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.4</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1730,7 +1718,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1743,7 +1731,7 @@
         <v>64.8</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1753,39 +1741,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1930,7 +1914,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1996,7 +1980,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2020,7 +2004,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>56</v>
+        <v>56.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2034,7 +2018,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2047,7 +2031,7 @@
         <v>64.8</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -2057,39 +2041,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2234,7 +2214,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2300,7 +2280,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2324,7 +2304,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>55.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2338,7 +2318,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2351,7 +2331,7 @@
         <v>64.8</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2361,39 +2341,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2538,7 +2514,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2604,7 +2580,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2628,7 +2604,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2642,7 +2618,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2655,7 +2631,7 @@
         <v>64.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2665,39 +2641,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2842,7 +2814,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2908,7 +2880,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2932,7 +2904,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2946,7 +2918,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2959,7 +2931,7 @@
         <v>64.8</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -2969,39 +2941,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3146,7 +3114,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3212,7 +3180,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3236,7 +3204,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3250,7 +3218,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3263,7 +3231,7 @@
         <v>64.8</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3273,39 +3241,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3450,7 +3414,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3516,7 +3480,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3540,7 +3504,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>51.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3554,7 +3518,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3567,7 +3531,7 @@
         <v>64.8</v>
       </c>
       <c r="S11" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3577,39 +3541,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3754,7 +3714,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3820,7 +3780,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3844,7 +3804,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3858,7 +3818,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3871,7 +3831,7 @@
         <v>64.8</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3881,39 +3841,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4058,7 +4014,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -4124,7 +4080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4148,7 +4104,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4162,7 +4118,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -4175,7 +4131,7 @@
         <v>64.8</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -4185,39 +4141,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4362,7 +4314,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4428,7 +4380,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4452,7 +4404,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>44.7</v>
+        <v>45.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4466,7 +4418,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4479,7 +4431,7 @@
         <v>64.8</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -4489,39 +4441,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4666,7 +4614,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4732,7 +4680,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4756,7 +4704,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4770,7 +4718,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4783,7 +4731,7 @@
         <v>64.8</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4793,39 +4741,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4970,7 +4914,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -5016,7 +4960,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gabriel Rincones</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5036,7 +4980,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5060,7 +5004,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5074,7 +5018,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -5087,7 +5031,7 @@
         <v>64.8</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -5097,39 +5041,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -5274,7 +5214,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5340,7 +5280,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5364,7 +5304,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5378,7 +5318,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5391,7 +5331,7 @@
         <v>64.8</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -5401,39 +5341,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5578,7 +5514,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5644,7 +5580,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5668,7 +5604,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5682,7 +5618,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -5695,7 +5631,7 @@
         <v>64.8</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -5705,39 +5641,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5882,7 +5814,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5948,7 +5880,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5972,7 +5904,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.8</v>
+        <v>36.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5986,7 +5918,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5999,7 +5931,7 @@
         <v>64.8</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
@@ -6009,39 +5941,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -6186,7 +6114,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6598,7 +6526,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6622,11 +6550,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6636,7 +6564,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6649,7 +6577,7 @@
         <v>64.8</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6659,39 +6587,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6836,7 +6760,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6902,7 +6826,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6926,7 +6850,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>68.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6940,7 +6864,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6953,7 +6877,7 @@
         <v>64.8</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6963,39 +6887,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7140,7 +7060,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -7206,7 +7126,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7230,7 +7150,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.7</v>
+        <v>57.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7244,7 +7164,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7257,7 +7177,7 @@
         <v>64.8</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>75</v>
@@ -7267,39 +7187,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7444,7 +7360,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7510,7 +7426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7534,7 +7450,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.4</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7548,7 +7464,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7561,7 +7477,7 @@
         <v>64.8</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -7571,39 +7487,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7748,7 +7660,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7814,7 +7726,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7838,7 +7750,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>56</v>
+        <v>56.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7852,7 +7764,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7865,7 +7777,7 @@
         <v>64.8</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7875,39 +7787,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -8052,7 +7960,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -8118,7 +8026,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8142,7 +8050,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>55.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8156,7 +8064,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8169,7 +8077,7 @@
         <v>64.8</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -8179,39 +8087,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8356,7 +8260,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -8422,7 +8326,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8446,7 +8350,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8460,7 +8364,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -8473,7 +8377,7 @@
         <v>64.8</v>
       </c>
       <c r="S8" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -8483,39 +8387,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8660,7 +8560,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8726,7 +8626,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8750,7 +8650,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8764,7 +8664,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8777,7 +8677,7 @@
         <v>64.8</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -8787,39 +8687,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8964,7 +8860,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -9030,7 +8926,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9054,7 +8950,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9068,7 +8964,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9081,7 +8977,7 @@
         <v>64.8</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -9091,39 +8987,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9268,7 +9160,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -9334,7 +9226,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9358,7 +9250,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>51</v>
+        <v>51.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9372,7 +9264,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9385,7 +9277,7 @@
         <v>64.8</v>
       </c>
       <c r="S11" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -9395,39 +9287,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9572,7 +9460,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -9638,7 +9526,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9662,7 +9550,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9676,7 +9564,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -9689,7 +9577,7 @@
         <v>64.8</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -9699,39 +9587,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9876,7 +9760,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9942,7 +9826,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9966,7 +9850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9980,7 +9864,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9993,7 +9877,7 @@
         <v>64.8</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -10003,39 +9887,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10180,7 +10060,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -10246,7 +10126,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10270,7 +10150,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>44.7</v>
+        <v>45.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10284,7 +10164,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10297,7 +10177,7 @@
         <v>64.8</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
@@ -10307,39 +10187,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10484,7 +10360,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -10550,7 +10426,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10574,7 +10450,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10588,7 +10464,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -10601,7 +10477,7 @@
         <v>64.8</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -10611,39 +10487,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10788,7 +10660,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10834,7 +10706,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gabriel Rincones</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10854,7 +10726,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10878,7 +10750,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10892,7 +10764,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -10905,7 +10777,7 @@
         <v>64.8</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
@@ -10915,39 +10787,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -11092,7 +10960,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -11158,7 +11026,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -11182,7 +11050,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11196,7 +11064,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -11209,7 +11077,7 @@
         <v>64.8</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>50</v>
@@ -11219,39 +11087,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11396,7 +11260,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -11462,7 +11326,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11486,7 +11350,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11500,7 +11364,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -11513,7 +11377,7 @@
         <v>64.8</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
@@ -11523,39 +11387,35 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11700,7 +11560,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -11766,7 +11626,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11790,7 +11650,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.8</v>
+        <v>36.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11804,7 +11664,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11817,7 +11677,7 @@
         <v>64.8</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
@@ -11827,39 +11687,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -12004,7 +11860,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>338 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-07-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-16.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16T23:10:00Z</t>
+          <t>2026-07-16T22:10:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
